--- a/output/graficos_regionales/plot_i_ingr_a_2020_la_araucania.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2020_la_araucania.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="C10">

--- a/output/graficos_regionales/plot_i_ingr_a_2020_la_araucania.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2020_la_araucania.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$G$18</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:46</t>
+    <t xml:space="preserve">2026-08-15 23:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -885,8 +885,27 @@
         <v>1066102.38</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>898522.25</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>856472.56</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales/plot_i_ingr_a_2020_la_araucania.xlsx
+++ b/output/graficos_regionales/plot_i_ingr_a_2020_la_araucania.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-15 23:23</t>
+    <t xml:space="preserve">2026-09-07 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
